--- a/datos_limpios/dic_fr_comp_DW.xlsx
+++ b/datos_limpios/dic_fr_comp_DW.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -379,34 +379,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sexo</t>
+          <t>anio</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sexo biológico</t>
+          <t>Año de registro</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>factor</t>
+          <t>numeric</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Mujer, Varón</t>
+          <t>0-Inf</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>grupo_edad_10</t>
+          <t>sexo</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Grupo de edad decenal</t>
+          <t>Sexo biológico</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -416,19 +416,19 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0 a 9, 10 a 19, 20 a 29, 30 a 39, 40 a 49, 50 a 59, 60 a 69, 70 a 79, 80+</t>
+          <t>Mujer, Varón</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>comp_tipo</t>
+          <t>grupo_edad_10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tipo de complicación crónica</t>
+          <t>Grupo de edad decenal</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -438,19 +438,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>macrovascular, microvascular</t>
+          <t>0 a 9, 10 a 19, 20 a 29, 30 a 39, 40 a 49, 50 a 59, 60 a 69, 70 a 79, 80+</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>comp_qualidiab</t>
+          <t>comp_tipo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nombre de la complicación crónica</t>
+          <t>Tipo de complicación crónica</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -460,49 +460,71 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ACV, Amputación, Ceguera, Claudicación miembros inferiores, Disfunción eréctil, IAM, IC, Nefropatía, Neuropatía periférica, Retinopatía no proliferativa, Retinopatía proliferativa, Sin complicaciones</t>
+          <t>macrovascular, microvascular</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>comp_frec</t>
+          <t>comp_qualidiab</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Frecuencia de la complicación crónica según sexo y grupo etario</t>
+          <t>Nombre de la complicación crónica</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>factor</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0-Inf</t>
+          <t>ACV, Amputación, Ceguera, Claudicación miembros inferiores, Disfunción eréctil, IAM, IC, Nefropatía, Neuropatía periférica, Retinopatía no proliferativa, Retinopatía proliferativa, Sin complicaciones</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>comp_frec</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Frecuencia de la complicación crónica según sexo y grupo etario</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>dw</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Peso de discapacidad asociado a la complicación</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>numeric</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>0-Inf</t>
         </is>
